--- a/labeled/Add_Eating/July/multi_seed_results/seed_456/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_456/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,1162 +442,746 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70.47618865966797</v>
+        <v>10.83743858337402</v>
       </c>
       <c r="B2" t="n">
-        <v>57.63059234619141</v>
+        <v>21.23198509216309</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6.660137176513672</v>
+        <v>32.41919708251953</v>
       </c>
       <c r="B3" t="n">
-        <v>13.11015129089355</v>
+        <v>19.0591926574707</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>24.10000038146973</v>
+        <v>11.4285717010498</v>
       </c>
       <c r="B4" t="n">
-        <v>17.45218276977539</v>
+        <v>14.41750907897949</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13.71204662322998</v>
+        <v>9.5</v>
       </c>
       <c r="B5" t="n">
-        <v>18.3096866607666</v>
+        <v>62.14508438110352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16.96428489685059</v>
+        <v>6.94444465637207</v>
       </c>
       <c r="B6" t="n">
-        <v>15.53247451782227</v>
+        <v>19.0956916809082</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>39.78174591064453</v>
+        <v>13.71204662322998</v>
       </c>
       <c r="B7" t="n">
-        <v>36.26500701904297</v>
+        <v>12.83887481689453</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17.70000076293945</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B8" t="n">
-        <v>13.83743762969971</v>
+        <v>26.84237098693848</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>28.5</v>
+        <v>15.118577003479</v>
       </c>
       <c r="B9" t="n">
-        <v>28.81969833374023</v>
+        <v>22.63971900939941</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14.18650817871094</v>
+        <v>141.6000061035156</v>
       </c>
       <c r="B10" t="n">
-        <v>13.37044429779053</v>
+        <v>125.1531600952148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40.09523773193359</v>
+        <v>26.15083312988281</v>
       </c>
       <c r="B11" t="n">
-        <v>22.96449279785156</v>
+        <v>27.81112480163574</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24.19047546386719</v>
+        <v>11.70634937286377</v>
       </c>
       <c r="B12" t="n">
-        <v>22.1373233795166</v>
+        <v>15.95901107788086</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>37.59999847412109</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="B13" t="n">
-        <v>31.80878639221191</v>
+        <v>19.63604164123535</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>40.47618865966797</v>
+        <v>46.5</v>
       </c>
       <c r="B14" t="n">
-        <v>24.24041938781738</v>
+        <v>37.03502655029297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21.5475025177002</v>
+        <v>20.4761905670166</v>
       </c>
       <c r="B15" t="n">
-        <v>24.55750274658203</v>
+        <v>29.1029224395752</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20.38095283508301</v>
+        <v>45.52381134033203</v>
       </c>
       <c r="B16" t="n">
-        <v>16.22997856140137</v>
+        <v>40.77235794067383</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12.99603176116943</v>
+        <v>68.5</v>
       </c>
       <c r="B17" t="n">
-        <v>11.92873001098633</v>
+        <v>69.72566986083984</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36.63075256347656</v>
+        <v>33.63095092773438</v>
       </c>
       <c r="B18" t="n">
-        <v>32.66640090942383</v>
+        <v>23.52389717102051</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19.5</v>
+        <v>18.31537628173828</v>
       </c>
       <c r="B19" t="n">
-        <v>13.08890342712402</v>
+        <v>12.67840385437012</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>26.44466209411621</v>
+        <v>46.79999923706055</v>
       </c>
       <c r="B20" t="n">
-        <v>23.38668441772461</v>
+        <v>46.42463302612305</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>44.70000076293945</v>
+        <v>17.53183174133301</v>
       </c>
       <c r="B21" t="n">
-        <v>40.68769073486328</v>
+        <v>13.03926658630371</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20.73412704467773</v>
+        <v>13.32027435302734</v>
       </c>
       <c r="B22" t="n">
-        <v>18.00081634521484</v>
+        <v>19.48615837097168</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40.27777862548828</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
-        <v>13.5344409942627</v>
+        <v>7.771527767181396</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>58.76591491699219</v>
+        <v>11.50793647766113</v>
       </c>
       <c r="B24" t="n">
-        <v>50.22951507568359</v>
+        <v>20.69497871398926</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>57.14285659790039</v>
+        <v>36.29999923706055</v>
       </c>
       <c r="B25" t="n">
-        <v>60.3463020324707</v>
+        <v>60.67990875244141</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>44.57143020629883</v>
+        <v>11.65524005889893</v>
       </c>
       <c r="B26" t="n">
-        <v>44.82915496826172</v>
+        <v>14.45262145996094</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6.502462863922119</v>
+        <v>12.2857141494751</v>
       </c>
       <c r="B27" t="n">
-        <v>5.168087959289551</v>
+        <v>17.38748931884766</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>46.20000076293945</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="B28" t="n">
-        <v>32.87792587280273</v>
+        <v>22.08774757385254</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22.89999961853027</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B29" t="n">
-        <v>16.25393486022949</v>
+        <v>17.09060859680176</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>19.39275169372559</v>
+        <v>8.275861740112305</v>
       </c>
       <c r="B30" t="n">
-        <v>18.56938934326172</v>
+        <v>22.84947776794434</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>23.80952453613281</v>
+        <v>39.09999847412109</v>
       </c>
       <c r="B31" t="n">
-        <v>22.23837280273438</v>
+        <v>46.01003265380859</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>58</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="B32" t="n">
-        <v>52.45930862426758</v>
+        <v>23.88089942932129</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>23.10000038146973</v>
+        <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>21.58341026306152</v>
+        <v>26.50342559814453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>29.39999961853027</v>
+        <v>17.23800277709961</v>
       </c>
       <c r="B34" t="n">
-        <v>24.88356781005859</v>
+        <v>16.91850471496582</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>59.52381134033203</v>
+        <v>9.304603576660156</v>
       </c>
       <c r="B35" t="n">
-        <v>60.88259887695312</v>
+        <v>10.92170906066895</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20.33730125427246</v>
+        <v>28.7952995300293</v>
       </c>
       <c r="B36" t="n">
-        <v>16.54121780395508</v>
+        <v>29.49966621398926</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>17.36111068725586</v>
+        <v>44.79999923706055</v>
       </c>
       <c r="B37" t="n">
-        <v>24.95660209655762</v>
+        <v>47.55593490600586</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>21.84133148193359</v>
+        <v>28</v>
       </c>
       <c r="B38" t="n">
-        <v>18.73478126525879</v>
+        <v>28.71517562866211</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>27.90476226806641</v>
+        <v>20.66601371765137</v>
       </c>
       <c r="B39" t="n">
-        <v>26.28965187072754</v>
+        <v>18.32709884643555</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20.27424049377441</v>
+        <v>12.5</v>
       </c>
       <c r="B40" t="n">
-        <v>22.46808242797852</v>
+        <v>11.80368041992188</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>79.36508178710938</v>
+        <v>54.66666793823242</v>
       </c>
       <c r="B41" t="n">
-        <v>75.96399688720703</v>
+        <v>51.52261734008789</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>100</v>
+        <v>39.5</v>
       </c>
       <c r="B42" t="n">
-        <v>93.58914947509766</v>
+        <v>42.2421875</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24.5714282989502</v>
+        <v>16.56746101379395</v>
       </c>
       <c r="B43" t="n">
-        <v>21.12160491943359</v>
+        <v>10.67913436889648</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>29.90476226806641</v>
+        <v>2.154750347137451</v>
       </c>
       <c r="B44" t="n">
-        <v>20.69460105895996</v>
+        <v>31.22644233703613</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>26.05288887023926</v>
+        <v>11.33333301544189</v>
       </c>
       <c r="B45" t="n">
-        <v>27.2911205291748</v>
+        <v>11.85708618164062</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>27.23809432983398</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="B46" t="n">
-        <v>18.81614112854004</v>
+        <v>11.87556457519531</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19.79999923706055</v>
+        <v>51.59999847412109</v>
       </c>
       <c r="B47" t="n">
-        <v>18.78057289123535</v>
+        <v>33.20455169677734</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>30.85210609436035</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="B48" t="n">
-        <v>20.7669563293457</v>
+        <v>18.12043952941895</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>40.20000076293945</v>
+        <v>26.34671974182129</v>
       </c>
       <c r="B49" t="n">
-        <v>35.60379028320312</v>
+        <v>27.62168502807617</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>11.11111068725586</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="B50" t="n">
-        <v>9.050044059753418</v>
+        <v>38.1327018737793</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>8.380952835083008</v>
+        <v>14.39764976501465</v>
       </c>
       <c r="B51" t="n">
-        <v>37.5498161315918</v>
+        <v>16.75325012207031</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>14.19999980926514</v>
+        <v>63.17335891723633</v>
       </c>
       <c r="B52" t="n">
-        <v>16.81729698181152</v>
+        <v>56.71730422973633</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>11.65524005889893</v>
+        <v>36.5</v>
       </c>
       <c r="B53" t="n">
-        <v>14.94774627685547</v>
+        <v>42.00494384765625</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>32.41919708251953</v>
+        <v>33.90000152587891</v>
       </c>
       <c r="B54" t="n">
-        <v>35.00296020507812</v>
+        <v>12.51582336425781</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>76.19047546386719</v>
+        <v>60</v>
       </c>
       <c r="B55" t="n">
-        <v>75.74338531494141</v>
+        <v>61.89831161499023</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20.33730125427246</v>
+        <v>19.19686508178711</v>
       </c>
       <c r="B56" t="n">
-        <v>19.06512641906738</v>
+        <v>24.12730598449707</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>31</v>
+        <v>40.47618865966797</v>
       </c>
       <c r="B57" t="n">
-        <v>25.70084762573242</v>
+        <v>22.61228179931641</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>43.79999923706055</v>
+        <v>26.98412704467773</v>
       </c>
       <c r="B58" t="n">
-        <v>43.76404190063477</v>
+        <v>13.28930473327637</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>13.88888931274414</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="B59" t="n">
-        <v>10.32899761199951</v>
+        <v>79.92109680175781</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>100</v>
+        <v>22.51984214782715</v>
       </c>
       <c r="B60" t="n">
-        <v>125.331901550293</v>
+        <v>21.83894729614258</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>27.79999923706055</v>
+        <v>35.16160583496094</v>
       </c>
       <c r="B61" t="n">
-        <v>17.10718154907227</v>
+        <v>27.08827209472656</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>45.52381134033203</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="B62" t="n">
-        <v>39.02872467041016</v>
+        <v>14.84874153137207</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>99.20635223388672</v>
+        <v>20.27424049377441</v>
       </c>
       <c r="B63" t="n">
-        <v>97.10353851318359</v>
+        <v>22.71223258972168</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>79.36508178710938</v>
+        <v>23</v>
       </c>
       <c r="B64" t="n">
-        <v>76.44402313232422</v>
+        <v>31.34357070922852</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>32.41919708251953</v>
+        <v>29.90476226806641</v>
       </c>
       <c r="B65" t="n">
-        <v>35.00296020507812</v>
+        <v>21.18855857849121</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>11.4285717010498</v>
+        <v>28.40352630615234</v>
       </c>
       <c r="B66" t="n">
-        <v>8.85806941986084</v>
+        <v>22.78125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>25.46523094177246</v>
+        <v>33.5</v>
       </c>
       <c r="B67" t="n">
-        <v>23.87082290649414</v>
+        <v>31.77362442016602</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>25.75905990600586</v>
+        <v>24.5714282989502</v>
       </c>
       <c r="B68" t="n">
-        <v>22.78416061401367</v>
+        <v>20.21293449401855</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>6.94444465637207</v>
+        <v>24.00793647766113</v>
       </c>
       <c r="B69" t="n">
-        <v>8.116836547851562</v>
+        <v>23.87438583374023</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>40</v>
+        <v>30.55827713012695</v>
       </c>
       <c r="B70" t="n">
-        <v>37.24230194091797</v>
+        <v>29.71040344238281</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>39.17727661132812</v>
+        <v>11.7142858505249</v>
       </c>
       <c r="B71" t="n">
-        <v>32.12076187133789</v>
+        <v>12.87671852111816</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>46.59999847412109</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B72" t="n">
-        <v>40.77969360351562</v>
+        <v>22.05731773376465</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>26.15083312988281</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="B73" t="n">
-        <v>25.24735832214355</v>
+        <v>14.93132591247559</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>60</v>
+        <v>19.5</v>
       </c>
       <c r="B74" t="n">
-        <v>54.83452224731445</v>
+        <v>14.9238395690918</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>60</v>
+        <v>15.47502422332764</v>
       </c>
       <c r="B75" t="n">
-        <v>42.6334228515625</v>
+        <v>12.89728546142578</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6.502462863922119</v>
+        <v>9.809523582458496</v>
       </c>
       <c r="B76" t="n">
-        <v>5.793503284454346</v>
+        <v>47.29021072387695</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>27.81586647033691</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B77" t="n">
-        <v>22.13127899169922</v>
+        <v>27.44292068481445</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>33.63095092773438</v>
+        <v>12.54940700531006</v>
       </c>
       <c r="B78" t="n">
-        <v>32.46944808959961</v>
+        <v>21.89290046691895</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>18.31537628173828</v>
+        <v>14.22924900054932</v>
       </c>
       <c r="B79" t="n">
-        <v>16.09953498840332</v>
+        <v>11.76317405700684</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>60</v>
+        <v>6.502462863922119</v>
       </c>
       <c r="B80" t="n">
-        <v>56.63495635986328</v>
+        <v>12.35419654846191</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>59.52381134033203</v>
+        <v>25.75905990600586</v>
       </c>
       <c r="B81" t="n">
-        <v>56.88886642456055</v>
+        <v>25.70758438110352</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>19.58863830566406</v>
+        <v>40.25465393066406</v>
       </c>
       <c r="B82" t="n">
-        <v>26.64549446105957</v>
+        <v>42.34577941894531</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>11.50793647766113</v>
+        <v>61</v>
       </c>
       <c r="B83" t="n">
-        <v>10.97279453277588</v>
+        <v>60.47464370727539</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>36.29999923706055</v>
+        <v>11.2380952835083</v>
       </c>
       <c r="B84" t="n">
-        <v>37.34182357788086</v>
+        <v>13.4047966003418</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>11.65524005889893</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="B85" t="n">
-        <v>12.79459476470947</v>
+        <v>25.66232681274414</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>9.027777671813965</v>
+        <v>8.630952835083008</v>
       </c>
       <c r="B86" t="n">
-        <v>8.491316795349121</v>
+        <v>10.79293251037598</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>9.06403923034668</v>
+        <v>34.5</v>
       </c>
       <c r="B87" t="n">
-        <v>8.088749885559082</v>
+        <v>23.48426246643066</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>24.87757110595703</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="B88" t="n">
-        <v>23.74535751342773</v>
+        <v>22.29965591430664</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>26.05288887023926</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="B89" t="n">
-        <v>24.99449157714844</v>
+        <v>11.17873191833496</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>16.5714282989502</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B90" t="n">
-        <v>18.80552864074707</v>
+        <v>15.86890029907227</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>8.275861740112305</v>
+        <v>18.4761905670166</v>
       </c>
       <c r="B91" t="n">
-        <v>8.659511566162109</v>
+        <v>18.51540565490723</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>38.09999847412109</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B92" t="n">
-        <v>36.61993408203125</v>
+        <v>20.24651336669922</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>12.54940700531006</v>
+        <v>57.20000076293945</v>
       </c>
       <c r="B93" t="n">
-        <v>15.99537944793701</v>
+        <v>60.93284606933594</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>59.52381134033203</v>
+        <v>16.38095283508301</v>
       </c>
       <c r="B94" t="n">
-        <v>71.30462646484375</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>20.47012710571289</v>
-      </c>
-      <c r="B95" t="n">
-        <v>19.87697219848633</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>15.0476188659668</v>
-      </c>
-      <c r="B96" t="n">
-        <v>13.53977298736572</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>20.66601371765137</v>
-      </c>
-      <c r="B97" t="n">
-        <v>21.8068790435791</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="B98" t="n">
-        <v>11.46665382385254</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>54.66666793823242</v>
-      </c>
-      <c r="B99" t="n">
-        <v>53.09022903442383</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="B100" t="n">
-        <v>45.25931930541992</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>28</v>
-      </c>
-      <c r="B101" t="n">
-        <v>25.23283958435059</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>2.154750347137451</v>
-      </c>
-      <c r="B102" t="n">
-        <v>9.086929321289062</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>8.380952835083008</v>
-      </c>
-      <c r="B103" t="n">
-        <v>37.5498161315918</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>80</v>
-      </c>
-      <c r="B104" t="n">
-        <v>78.93523406982422</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>59.40000152587891</v>
-      </c>
-      <c r="B105" t="n">
-        <v>54.72124099731445</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>92.90000152587891</v>
-      </c>
-      <c r="B106" t="n">
-        <v>90.00593566894531</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>87.80000305175781</v>
-      </c>
-      <c r="B107" t="n">
-        <v>84.91697692871094</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>23.21428489685059</v>
-      </c>
-      <c r="B108" t="n">
-        <v>15.50226211547852</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>60</v>
-      </c>
-      <c r="B109" t="n">
-        <v>62.80187606811523</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>79.36508178710938</v>
-      </c>
-      <c r="B110" t="n">
-        <v>74.49002838134766</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>26.98412704467773</v>
-      </c>
-      <c r="B111" t="n">
-        <v>18.03977394104004</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>97.94319152832031</v>
-      </c>
-      <c r="B112" t="n">
-        <v>103.549934387207</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>11.43984222412109</v>
-      </c>
-      <c r="B113" t="n">
-        <v>12.28671360015869</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>16.39999961853027</v>
-      </c>
-      <c r="B114" t="n">
-        <v>15.3683443069458</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>20.27424049377441</v>
-      </c>
-      <c r="B115" t="n">
-        <v>22.46808242797852</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>17.53183174133301</v>
-      </c>
-      <c r="B116" t="n">
-        <v>10.020263671875</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>20</v>
-      </c>
-      <c r="B117" t="n">
-        <v>23.1395149230957</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>28.40352630615234</v>
-      </c>
-      <c r="B118" t="n">
-        <v>24.34123229980469</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>6.660137176513672</v>
-      </c>
-      <c r="B119" t="n">
-        <v>8.803808212280273</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="B120" t="n">
-        <v>24.97400665283203</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>25.09920692443848</v>
-      </c>
-      <c r="B121" t="n">
-        <v>22.21631622314453</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>24.00793647766113</v>
-      </c>
-      <c r="B122" t="n">
-        <v>18.18392944335938</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>30.66666603088379</v>
-      </c>
-      <c r="B123" t="n">
-        <v>26.26045989990234</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>30.55827713012695</v>
-      </c>
-      <c r="B124" t="n">
-        <v>29.59686851501465</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>6.646825313568115</v>
-      </c>
-      <c r="B125" t="n">
-        <v>4.443661212921143</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>20</v>
-      </c>
-      <c r="B126" t="n">
-        <v>36.28871536254883</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>9.809523582458496</v>
-      </c>
-      <c r="B127" t="n">
-        <v>12.79741764068604</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>23.5238094329834</v>
-      </c>
-      <c r="B128" t="n">
-        <v>23.54705619812012</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>12.54940700531006</v>
-      </c>
-      <c r="B129" t="n">
-        <v>15.99537944793701</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>14.22924900054932</v>
-      </c>
-      <c r="B130" t="n">
-        <v>14.53697299957275</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>6.502462863922119</v>
-      </c>
-      <c r="B131" t="n">
-        <v>5.793503284454346</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B132" t="n">
-        <v>33.07355117797852</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>36.29999923706055</v>
-      </c>
-      <c r="B133" t="n">
-        <v>37.34182357788086</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>11.2380952835083</v>
-      </c>
-      <c r="B134" t="n">
-        <v>14.94311237335205</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>9.189723014831543</v>
-      </c>
-      <c r="B135" t="n">
-        <v>9.305098533630371</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>8.630952835083008</v>
-      </c>
-      <c r="B136" t="n">
-        <v>9.488122940063477</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="B137" t="n">
-        <v>25.46016883850098</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>40</v>
-      </c>
-      <c r="B138" t="n">
-        <v>37.48007583618164</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>28.7952995300293</v>
-      </c>
-      <c r="B139" t="n">
-        <v>31.00008773803711</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>17.10000038146973</v>
-      </c>
-      <c r="B140" t="n">
-        <v>16.1701545715332</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>25.79999923706055</v>
-      </c>
-      <c r="B141" t="n">
-        <v>23.26577758789062</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>18.4761905670166</v>
-      </c>
-      <c r="B142" t="n">
-        <v>16.74323654174805</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>68.28571319580078</v>
-      </c>
-      <c r="B143" t="n">
-        <v>65.49921417236328</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>160.1999969482422</v>
-      </c>
-      <c r="B144" t="n">
-        <v>155.1854858398438</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>15.51383399963379</v>
-      </c>
-      <c r="B145" t="n">
-        <v>18.4371280670166</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>18.65079307556152</v>
-      </c>
-      <c r="B146" t="n">
-        <v>15.52739334106445</v>
+        <v>15.61556625366211</v>
       </c>
     </row>
   </sheetData>
